--- a/output/(山本)規範適合性_基準適合性_再構成.xlsx
+++ b/output/(山本)規範適合性_基準適合性_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,13 +461,13 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>職務分掌規程等の組織内規に定義された承認権限や職位を、システム上のロール（役割）および操作権限（参照・更新・承認等）へ具体的に対応付けて記述している。</t>
+          <t>業務フロー図や職務権限規程などの上位要件に基づき、各機能における利用者のアクセス権限、およびデータ操作範囲（参照、登録、更新、削除）の制御仕様を明記している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】発注機能の権限設計において、職能に関わらず一律の権限を付与しているため、担当者が自身の入力を自己承認できる状態になっている。(牽制機能の欠如)
-→【適合例】職務分掌規程に基づき、発注入力者と発注承認者のロールを分離し、同一ユーザーによる自己承認を制限する制御を記述する。</t>
+          <t>【非適合例】システム利用者は誰でも発注処理を実行できる仕様になっている。（職務分掌に基づく権限制御が定義されていない。）
+→【適合例】職務権限規程に基づき、購買部の所属ユーザーのみが発注処理を実行できるようにアクセス権限の制御仕様を定義している。</t>
         </is>
       </c>
     </row>
@@ -479,14 +479,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>サービス展開対象となる各国の法令、公的規格（排出ガス、電磁波、安全性等）、および商習慣を特定し、各仕向地の要件を個別に、または共通の最高水準で満たすための仕様を記述している。</t>
+          <t>システムを導入または展開する対象国および地域の法令、各種規制、業界標準などの要件を特定し、仕向地ごとの基準値を満たすパラメータや制御仕様を明記している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】無線通信仕様を日本国内の電波法のみに準拠させて設計したため、欧州等の海外市場で利用できない仕様となっている。(特定地域のみの考慮)
-→【適合例】無線通信仕様において、日本、米国、および欧州(CEマーク等)の各電波規制を調査し、全対象国の基準を同時に充足する周波数帯および出力仕様を記述する。</t>
+【非適合例】エンジン制御システムにおいて、自動車排出ガスが日本国内の基準値のみを満たす仕様となっている。（対象国の規制が考慮されていない。）
+→【適合例】エンジン制御システムにおいて、自動車排出ガスが北米および欧州の環境規制値（EURO6など）を満たすように、仕向地別のパラメータ制御仕様を定義している。</t>
         </is>
       </c>
     </row>
@@ -498,13 +498,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>時差、通貨、多言語対応、および国際的な識別体系（国番号付き電話番号、タイムゾーン、ISO通貨コード等）を考慮し、場所を問わず利用可能なインタフェース仕様を記述している。</t>
+          <t>グローバルに展開するサービスにおいて、現地要件（タイムゾーン、現地通貨、多言語対応、現地の連絡先など）を考慮し、対象国の利用者がシステムを支障なく利用できる仕様として明記している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】システム内の日付表示が日本標準時(JST)固定であり、海外拠点から利用した際に現地時間との整合が取れない。(タイムゾーンの未考慮)
-→【適合例】表示時刻の仕様において、ユーザーの現在地に応じたタイムゾーン変換機能を定義し、UTC(協定世界時)とのオフセット値を明記する。</t>
+          <t>★新規追加
+【非適合例】海外向けサービスのサポート窓口として、日本国内からのみ接続可能なフリーダイヤル番号を記載している。（現地からの利用可能性が考慮されていない。）
+→【適合例】海外向けサービスのサポート窓口として、対象国ごとに現地から無料で接続できるトールフリー番号を一覧表として明記している。</t>
         </is>
       </c>
     </row>
@@ -516,13 +517,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>実装する独自のアルゴリズムやUI、商標等について、第三者の知的財産権（特許・著作権）を侵害していないことを公的データベース等で調査し、その根拠と調査範囲を記述している。</t>
+          <t>採用する技術、アルゴリズム、および外部ライブラリについて、先行特許調査の結果やOSSライセンス規約に基づき、第三者の知的財産権を侵害していないことを確認した根拠を明記している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】特有のジェスチャーによる画面操作をUIに採用しているが、OSベンダーや競合他社の特許に抵触するかを確認していない。(特許侵害の懸念)
-→【適合例】新規採用するUIのジェスチャー操作について特許調査を実施し、特定された他社特許との差異を整理した上で、抵触しない判断根拠を記述する。</t>
+          <t>★新規追加
+【非適合例】新機能に用いるデータ圧縮アルゴリズムを採用する旨のみを記載している。（第三者の特許を侵害していないかどうかの根拠が欠落している。）
+→【適合例】新機能に用いるデータ圧縮アルゴリズムについて、特許庁データベースを用いた先行特許調査を実施し、他社の権利を侵害していないことを確認した結果を別紙として添付している。</t>
         </is>
       </c>
     </row>
@@ -534,14 +536,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>適用対象となる法律（個人情報保護法、GDPR等）や業界ガイドライン（PCI DSS、ISMS等）を特定し、データの暗号化方式、保持期間、廃棄手順等の具体的な保護要件を記述している。</t>
+          <t>システムが取り扱う機密データ（個人情報やクレジットカード情報など）について、個人情報保護法やISMSなどのセキュリティ基準に基づき、暗号化方式やアクセス制御などの保護仕様を明記している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】クレジットカード情報を保存するデータベースの設計において、データの暗号化方式や鍵管理の手順が定められていない。(セキュリティ基準の無視)
-→【適合例】PCI DSSの基準に準拠し、クレジットカード番号のAES-256による暗号化、および暗号鍵の定期的な更新手順を設計書に記述する。</t>
+【非適合例】ユーザー情報を格納するデータベースの仕様において、暗号化やアクセス制御の方法が定義されていない。（セキュリティ基準に基づく保護仕様が欠落している。）
+→【適合例】ユーザー情報を格納するデータベースの仕様において、組織のセキュリティガイドラインに基づき、保存データにAES-256を用いた暗号化を適用する仕様を明記している。</t>
         </is>
       </c>
     </row>
@@ -553,13 +555,14 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>文書体系図や執筆要領（規約）に定められた、階層構造（WBS/章構成）、フォントサイズ、表記ゆれの禁止ルール、および必須記述項目をすべて充足していることを記述している。</t>
+          <t>組織やプロジェクトが規定する文書テンプレートを採用し、指定された章立て、見出し構成、および入力フォーマット（フォント、表の形式など）に準拠して各項目を記述している。</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】プロジェクトで配布された設計書テンプレートを使用せず、過去の別案件の形式を流用したため、必須項目である「非機能要件」の章が欠落している。(標準構成の逸脱)
-→【適合例】最新の文書構成案に基づき、テンプレートの全項目を網羅し、見出しレベルやインデント等の書式ルールを統一して記述する。</t>
+          <t>★新規追加
+【非適合例】基本設計書において、プロジェクト標準のテンプレートを使用せず、担当者が独自の章立てで機能要件を記述している。（文書構造の標準化が損なわれている。）
+→【適合例】プロジェクト標準の基本設計書テンプレートを採用し、規定された章立ておよびフォーマットに従って機能要件を記述している。</t>
         </is>
       </c>
     </row>
@@ -571,14 +574,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>外部仕様書、法令、業界標準規格等を引用する際、参照先の一意性が保たれるよう、正式名称、版数（バージョン）、発行日、および該当セクションを漏れなく記述している。</t>
+          <t>外部資料や他システムの仕様書から情報を引用または参照する場合、トレーサビリティを確保するために、対象となる文書名、発行元、バージョン、および該当箇所（章番号など）を明記している。</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】暗号化通信の仕様について「最新のTLS規格に従う」と記述しているが、具体的なバージョンやRFC番号の指定がない。(参照情報の曖昧性)
-→【適合例】通信プロトコルの仕様について「IETF発行のRFC8446(Transport Layer Security(TLS)Protocol Version 1.3)」を準拠先として明記する。</t>
+【非適合例】外部連携APIの仕様に関する記述において、公式ドキュメントへのリンクのみが記載されている。（リンク切れの際にバージョンや該当箇所が追跡できなくなる。）
+→【適合例】外部連携APIの仕様に関する記述において、提供元のA社が公開している「API連携仕様書（v2.0）の第3章」を情報源として明記している。</t>
         </is>
       </c>
     </row>
@@ -590,33 +593,14 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ログ、測定データ、確定した要件、ハードウェアの定格仕様などの証跡がある「事実」については、「〜である」「〜を確認した」と、主観を排除した断定的な形式で記述している。</t>
+          <t>客観的に確認可能な事象（システムログ、テスト結果、法令の制約など）と、主観的な判断（推測、対応方針の提案、設計者の見解など）を混同せず、文脈または項目の切り分けによって明確に分離して記述している。</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】性能試験の結果について、「サーバーの負荷は概ね許容範囲内にあると考えられる」と記述し、具体的な測定値の記載を省略している。(事実の曖昧な記述)
-→【適合例】性能試験の結果について、「同時接続1,000ユーザー時のCPU使用率は最大45%であり、目標値の60%以下を達成した」と証跡に基づき記述する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>事実と意見を書き分けている</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>設計の選択理由、未確定の推論、今後の対応方針などの「意見・判断」については、「〜と判断する」「〜を推奨する」といった表現を用い、事実と明確に区別して記述している。</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>★新規追加
-【非適合例】代替案の検討において、特定のライブラリを採用する旨が結論のみ記載されており、選定に至った設計者の意図が不明である。(判断プロセスの隠蔽)
-→【適合例】「将来的な保守性の観点から、独自実装ではなくOSSのXXライブラリを採用することが妥当であると判断した」という設計意図を、仕様とは別の「選定理由」項に記述する。</t>
+【非適合例】負荷テストでメモリ不足による処理遅延が発生しているため、本番環境のサーバースペックをスケールアップすべきである。（事象の報告と対応方針の提案が連続して書かれており、事実と意見の境界が不明確である。）
+→【適合例】事実として、負荷テストにおいてメモリ使用率が95%を超過し処理遅延が発生した結果を記載し、その事象に対する対応方針の意見として、本番環境のサーバースペックをスケールアップする旨を別の項目に分けて明記している。</t>
         </is>
       </c>
     </row>
